--- a/template/master_peserta.xlsx
+++ b/template/master_peserta.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\prsc\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C5226F9F-538B-4DF2-93D6-F7A829C328B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98C14C57-2505-4FEB-98C8-7629C8B5E68A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7BF0C0D1-1B08-4AA2-9143-3B8775208860}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="peserta" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="92">
   <si>
     <t>nik</t>
   </si>
@@ -282,6 +282,36 @@
   </si>
   <si>
     <t>SSPE3</t>
+  </si>
+  <si>
+    <t>KLP1 ADMN</t>
+  </si>
+  <si>
+    <t>KLP1 MILL</t>
+  </si>
+  <si>
+    <t>MBKM-MSIB</t>
+  </si>
+  <si>
+    <t>MAGANG AKPY</t>
+  </si>
+  <si>
+    <t>PKL SMK</t>
+  </si>
+  <si>
+    <t>KLP1 ADMN 19-2025</t>
+  </si>
+  <si>
+    <t>KLP1 MILL 19-2025</t>
+  </si>
+  <si>
+    <t>MSIB BATCH 8-2025</t>
+  </si>
+  <si>
+    <t>AKPY BATCH 9-2025</t>
+  </si>
+  <si>
+    <t>PKL SMK BATCH 3-2025</t>
   </si>
 </sst>
 </file>
@@ -663,7 +693,7 @@
     <col min="5" max="5" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.140625" customWidth="1"/>
-    <col min="8" max="8" width="18" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -804,7 +834,7 @@
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="D6">
         <v>2025</v>
@@ -819,7 +849,7 @@
         <v>25</v>
       </c>
       <c r="H6" t="s">
-        <v>13</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -830,7 +860,7 @@
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="D7">
         <v>2025</v>
@@ -845,7 +875,7 @@
         <v>25</v>
       </c>
       <c r="H7" t="s">
-        <v>13</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -856,7 +886,7 @@
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="D8">
         <v>2025</v>
@@ -871,7 +901,7 @@
         <v>25</v>
       </c>
       <c r="H8" t="s">
-        <v>13</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -882,7 +912,7 @@
         <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="D9">
         <v>2025</v>
@@ -897,7 +927,7 @@
         <v>25</v>
       </c>
       <c r="H9" t="s">
-        <v>13</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -908,7 +938,7 @@
         <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>9</v>
+        <v>83</v>
       </c>
       <c r="D10">
         <v>2025</v>
@@ -923,7 +953,7 @@
         <v>37</v>
       </c>
       <c r="H10" t="s">
-        <v>13</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -934,7 +964,7 @@
         <v>38</v>
       </c>
       <c r="C11" t="s">
-        <v>9</v>
+        <v>83</v>
       </c>
       <c r="D11">
         <v>2025</v>
@@ -949,7 +979,7 @@
         <v>37</v>
       </c>
       <c r="H11" t="s">
-        <v>13</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -960,7 +990,7 @@
         <v>41</v>
       </c>
       <c r="C12" t="s">
-        <v>9</v>
+        <v>83</v>
       </c>
       <c r="D12">
         <v>2025</v>
@@ -975,7 +1005,7 @@
         <v>37</v>
       </c>
       <c r="H12" t="s">
-        <v>13</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -986,7 +1016,7 @@
         <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>9</v>
+        <v>83</v>
       </c>
       <c r="D13">
         <v>2025</v>
@@ -1001,7 +1031,7 @@
         <v>37</v>
       </c>
       <c r="H13" t="s">
-        <v>13</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -1012,7 +1042,7 @@
         <v>47</v>
       </c>
       <c r="C14" t="s">
-        <v>9</v>
+        <v>84</v>
       </c>
       <c r="D14">
         <v>2025</v>
@@ -1027,7 +1057,7 @@
         <v>37</v>
       </c>
       <c r="H14" t="s">
-        <v>13</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -1038,7 +1068,7 @@
         <v>49</v>
       </c>
       <c r="C15" t="s">
-        <v>9</v>
+        <v>84</v>
       </c>
       <c r="D15">
         <v>2025</v>
@@ -1053,7 +1083,7 @@
         <v>52</v>
       </c>
       <c r="H15" t="s">
-        <v>13</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1064,7 +1094,7 @@
         <v>53</v>
       </c>
       <c r="C16" t="s">
-        <v>9</v>
+        <v>84</v>
       </c>
       <c r="D16">
         <v>2025</v>
@@ -1079,7 +1109,7 @@
         <v>52</v>
       </c>
       <c r="H16" t="s">
-        <v>13</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1090,7 +1120,7 @@
         <v>55</v>
       </c>
       <c r="C17" t="s">
-        <v>9</v>
+        <v>84</v>
       </c>
       <c r="D17">
         <v>2025</v>
@@ -1105,7 +1135,7 @@
         <v>52</v>
       </c>
       <c r="H17" t="s">
-        <v>13</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1116,7 +1146,7 @@
         <v>58</v>
       </c>
       <c r="C18" t="s">
-        <v>9</v>
+        <v>85</v>
       </c>
       <c r="D18">
         <v>2025</v>
@@ -1131,7 +1161,7 @@
         <v>52</v>
       </c>
       <c r="H18" t="s">
-        <v>13</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1142,7 +1172,7 @@
         <v>60</v>
       </c>
       <c r="C19" t="s">
-        <v>9</v>
+        <v>85</v>
       </c>
       <c r="D19">
         <v>2025</v>
@@ -1157,7 +1187,7 @@
         <v>52</v>
       </c>
       <c r="H19" t="s">
-        <v>13</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1168,7 +1198,7 @@
         <v>63</v>
       </c>
       <c r="C20" t="s">
-        <v>9</v>
+        <v>85</v>
       </c>
       <c r="D20">
         <v>2025</v>
@@ -1183,7 +1213,7 @@
         <v>52</v>
       </c>
       <c r="H20" t="s">
-        <v>13</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1194,7 +1224,7 @@
         <v>65</v>
       </c>
       <c r="C21" t="s">
-        <v>9</v>
+        <v>85</v>
       </c>
       <c r="D21">
         <v>2025</v>
@@ -1209,7 +1239,7 @@
         <v>68</v>
       </c>
       <c r="H21" t="s">
-        <v>13</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1220,7 +1250,7 @@
         <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>9</v>
+        <v>86</v>
       </c>
       <c r="D22">
         <v>2025</v>
@@ -1235,7 +1265,7 @@
         <v>68</v>
       </c>
       <c r="H22" t="s">
-        <v>13</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1246,7 +1276,7 @@
         <v>71</v>
       </c>
       <c r="C23" t="s">
-        <v>9</v>
+        <v>86</v>
       </c>
       <c r="D23">
         <v>2025</v>
@@ -1261,7 +1291,7 @@
         <v>68</v>
       </c>
       <c r="H23" t="s">
-        <v>13</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1272,7 +1302,7 @@
         <v>74</v>
       </c>
       <c r="C24" t="s">
-        <v>9</v>
+        <v>86</v>
       </c>
       <c r="D24">
         <v>2025</v>
@@ -1287,7 +1317,7 @@
         <v>68</v>
       </c>
       <c r="H24" t="s">
-        <v>13</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -1298,7 +1328,7 @@
         <v>77</v>
       </c>
       <c r="C25" t="s">
-        <v>9</v>
+        <v>86</v>
       </c>
       <c r="D25">
         <v>2025</v>
@@ -1313,7 +1343,7 @@
         <v>68</v>
       </c>
       <c r="H25" t="s">
-        <v>13</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -1324,7 +1354,7 @@
         <v>80</v>
       </c>
       <c r="C26" t="s">
-        <v>9</v>
+        <v>86</v>
       </c>
       <c r="D26">
         <v>2025</v>
@@ -1339,7 +1369,7 @@
         <v>68</v>
       </c>
       <c r="H26" t="s">
-        <v>13</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
